--- a/Result/profitability/1305.xlsx
+++ b/Result/profitability/1305.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>0.27</v>
       </c>
       <c r="M2" t="n">
-        <v>-0.35625</v>
+        <v>-0.2387499999999999</v>
       </c>
       <c r="N2" t="n">
-        <v>-1.53</v>
+        <v>1.61875</v>
       </c>
       <c r="O2" t="n">
         <v>1</v>
@@ -684,13 +684,13 @@
         <v>1</v>
       </c>
       <c r="R2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S2" t="n">
         <v>1</v>
       </c>
       <c r="T2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U2" t="n">
         <v>0</v>
@@ -780,10 +780,10 @@
         <v>0.63</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.1887499999999999</v>
+        <v>-0.08249999999999996</v>
       </c>
       <c r="N3" t="n">
-        <v>1.48375</v>
+        <v>3.4825</v>
       </c>
       <c r="O3" t="n">
         <v>1</v>
@@ -795,13 +795,13 @@
         <v>1</v>
       </c>
       <c r="R3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S3" t="n">
         <v>1</v>
       </c>
       <c r="T3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U3" t="n">
         <v>0</v>
@@ -899,10 +899,10 @@
         <v>0.17</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.08999999999999997</v>
+        <v>-0.003749999999999972</v>
       </c>
       <c r="N4" t="n">
-        <v>3.20375</v>
+        <v>5.62125</v>
       </c>
       <c r="O4" t="n">
         <v>1</v>
@@ -1018,10 +1018,10 @@
         <v>-1.84</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.2625</v>
+        <v>-0.14625</v>
       </c>
       <c r="N5" t="n">
-        <v>0.1837500000000003</v>
+        <v>2.96875</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1137,10 +1137,10 @@
         <v>0.63</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.09624999999999999</v>
+        <v>-0.045</v>
       </c>
       <c r="N6" t="n">
-        <v>3.82875</v>
+        <v>6.063750000000001</v>
       </c>
       <c r="O6" t="n">
         <v>1</v>
@@ -1264,10 +1264,10 @@
         <v>0.44</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.01874999999999998</v>
+        <v>0.04000000000000001</v>
       </c>
       <c r="N7" t="n">
-        <v>6.61375</v>
+        <v>8.41375</v>
       </c>
       <c r="O7" t="n">
         <v>1</v>
@@ -1391,10 +1391,10 @@
         <v>0.26</v>
       </c>
       <c r="M8" t="n">
-        <v>0.04375000000000001</v>
+        <v>0.09875</v>
       </c>
       <c r="N8" t="n">
-        <v>8.268750000000001</v>
+        <v>9.90375</v>
       </c>
       <c r="O8" t="n">
         <v>1</v>
@@ -1521,7 +1521,7 @@
         <v>0.05375000000000001</v>
       </c>
       <c r="N9" t="n">
-        <v>8.805</v>
+        <v>8.805000000000001</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
@@ -1902,7 +1902,7 @@
         <v>-0.09</v>
       </c>
       <c r="N12" t="n">
-        <v>6.947500000000001</v>
+        <v>6.9475</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
@@ -9830,6 +9830,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>1305</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>2730</v>
+      </c>
+      <c r="D75" t="n">
+        <v>2319</v>
+      </c>
+      <c r="E75" t="n">
+        <v>411</v>
+      </c>
+      <c r="F75" t="n">
+        <v>15.05</v>
+      </c>
+      <c r="G75" t="n">
+        <v>180</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>6.61%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>-19</v>
+      </c>
+      <c r="J75" t="n">
+        <v>161</v>
+      </c>
+      <c r="K75" t="n">
+        <v>133</v>
+      </c>
+      <c r="L75" t="n">
+        <v>0.23</v>
+      </c>
+      <c r="M75" t="n">
+        <v>-0.36125</v>
+      </c>
+      <c r="N75" t="n">
+        <v>-0.9700000000000002</v>
+      </c>
+      <c r="O75" t="n">
+        <v>1</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>1</v>
+      </c>
+      <c r="R75" t="n">
+        <v>1</v>
+      </c>
+      <c r="S75" t="n">
+        <v>1</v>
+      </c>
+      <c r="T75" t="n">
+        <v>1</v>
+      </c>
+      <c r="U75" t="n">
+        <v>0</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="X75" t="n">
+        <v>-2.095238095238095</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>13.08</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>6.639593908629442</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>0.9299999999999999</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>-1.328571428571429</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>22.28</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>-3.081604426002766</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率成長</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
